--- a/quizzes/049_monat_hair_quiz_ubb--quizzes.xlsx
+++ b/quizzes/049_monat_hair_quiz_ubb--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Page6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Page9</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Page10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Page11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Page12</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Page13</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Page14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Page15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Page16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Page17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Page18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Page19</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Page20</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Page21</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Page22</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Page23</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Page24</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Page25</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
